--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2756559D-9B1E-4425-A29C-65126A745DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8A4B31-409D-4071-966D-A76CBE9582B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -665,7 +665,7 @@
         <v>-7.5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>8.5</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8A4B31-409D-4071-966D-A76CBE9582B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491177FF-E8CB-41AD-B645-3F8BADF11C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -498,13 +498,13 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D2">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-7.5</v>
+        <v>-7</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -583,10 +583,10 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -621,10 +621,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="D5">
         <v>-7</v>
@@ -662,19 +662,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-7.5</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>8.5</v>
+        <v>-14</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -949,13 +949,13 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-2</v>
+        <v>7.5</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>0.5</v>
+        <v>-6.5</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1031,13 +1031,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1146,6 +1146,170 @@
         <v>0</v>
       </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>2.1</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>0.5</v>
+      </c>
+      <c r="J18">
+        <v>0.5</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>-25</v>
+      </c>
+      <c r="C19">
+        <v>2.1</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <v>0.5</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>-13</v>
+      </c>
+      <c r="C20">
+        <v>2.1</v>
+      </c>
+      <c r="D20">
+        <v>14</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>-13</v>
+      </c>
+      <c r="C21">
+        <v>2.1</v>
+      </c>
+      <c r="D21">
+        <v>-14</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491177FF-E8CB-41AD-B645-3F8BADF11C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8880F5-2FA0-44B4-819D-CEC405A714E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-10.5</v>
+        <v>-14.2</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>-10.5</v>
+        <v>-14.2</v>
       </c>
       <c r="E17">
         <v>0</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8880F5-2FA0-44B4-819D-CEC405A714E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3AF83D-B7F2-4A9B-B6FC-4B1F6D1BA02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1031,13 +1031,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="E15">
         <v>0</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3AF83D-B7F2-4A9B-B6FC-4B1F6D1BA02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D38C0E-9A16-4F73-8177-30549FE2E758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -662,19 +662,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>-14</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1231,47 +1231,6 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20">
-        <v>-13</v>
-      </c>
-      <c r="C20">
-        <v>2.1</v>
-      </c>
-      <c r="D20">
-        <v>14</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>16</v>
@@ -1310,6 +1269,47 @@
         <v>0</v>
       </c>
       <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>2.1</v>
+      </c>
+      <c r="D22">
+        <v>-14</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D38C0E-9A16-4F73-8177-30549FE2E758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8ED274-55C1-489F-8104-3D6CC5A1E388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -867,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>1</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8ED274-55C1-489F-8104-3D6CC5A1E388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C1F69B-BCF8-4A02-A522-9002CAB3F526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-5.5</v>
+        <v>-6.5</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -826,7 +826,7 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1231,6 +1231,47 @@
         <v>-10</v>
       </c>
     </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+      <c r="I20">
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <v>0.5</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>16</v>
@@ -1248,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1310,6 +1351,129 @@
         <v>0</v>
       </c>
       <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0.5</v>
+      </c>
+      <c r="I23">
+        <v>0.5</v>
+      </c>
+      <c r="J23">
+        <v>0.5</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>-13</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0.5</v>
+      </c>
+      <c r="I24">
+        <v>0.5</v>
+      </c>
+      <c r="J24">
+        <v>0.5</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0.5</v>
+      </c>
+      <c r="I25">
+        <v>0.5</v>
+      </c>
+      <c r="J25">
+        <v>0.5</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C1F69B-BCF8-4A02-A522-9002CAB3F526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FE7F79-D476-4BC4-B7C4-503C0292417D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,7 +665,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D6">
         <v>15</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FE7F79-D476-4BC4-B7C4-503C0292417D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59CCAC-8D0D-4D4A-AAB0-E82B9BED2CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,7 +668,7 @@
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>0</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59CCAC-8D0D-4D4A-AAB0-E82B9BED2CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B119DD-E272-4CFE-AE67-87B3F9137E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -662,7 +662,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>1.5</v>
@@ -826,7 +826,7 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -867,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -908,7 +908,7 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1113,7 +1113,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>-3</v>
+        <v>-4.5</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1318,7 +1318,7 @@
         <v>16</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C22">
         <v>2.1</v>
@@ -1441,13 +1441,13 @@
         <v>15</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1474,6 +1474,334 @@
         <v>0</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>19</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0.5</v>
+      </c>
+      <c r="I26">
+        <v>0.5</v>
+      </c>
+      <c r="J26">
+        <v>0.5</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>-19</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0.5</v>
+      </c>
+      <c r="I27">
+        <v>0.5</v>
+      </c>
+      <c r="J27">
+        <v>0.5</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>-19</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>18.5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0.5</v>
+      </c>
+      <c r="I28">
+        <v>0.5</v>
+      </c>
+      <c r="J28">
+        <v>0.5</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29">
+        <v>-9</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>-19</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0.5</v>
+      </c>
+      <c r="I29">
+        <v>0.5</v>
+      </c>
+      <c r="J29">
+        <v>0.5</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>-19</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0.5</v>
+      </c>
+      <c r="I30">
+        <v>0.5</v>
+      </c>
+      <c r="J30">
+        <v>0.5</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31">
+        <v>-18</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>-18</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0.5</v>
+      </c>
+      <c r="I31">
+        <v>0.5</v>
+      </c>
+      <c r="J31">
+        <v>0.5</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0.5</v>
+      </c>
+      <c r="I32">
+        <v>0.5</v>
+      </c>
+      <c r="J32">
+        <v>0.5</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>-14.2</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0.5</v>
+      </c>
+      <c r="I33">
+        <v>0.5</v>
+      </c>
+      <c r="J33">
+        <v>0.5</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B119DD-E272-4CFE-AE67-87B3F9137E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D963270-D696-43DA-9FBE-208D0D56C57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -668,13 +668,13 @@
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>-14</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>2.1</v>
       </c>
       <c r="D22">
-        <v>-14</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>0</v>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D963270-D696-43DA-9FBE-208D0D56C57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C699678-DB96-45F7-AB32-C761E3144B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="795" windowWidth="21600" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -498,7 +498,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>2.1</v>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="C3">
         <v>2.1</v>
@@ -586,7 +586,7 @@
         <v>2.1</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>2.1</v>
       </c>
       <c r="D5">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -662,13 +662,13 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>-12.5</v>
       </c>
       <c r="C6">
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         <v>15</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1646,13 +1646,13 @@
         <v>15</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>-19</v>
+        <v>-19.5</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1802,6 +1802,47 @@
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34">
+        <v>11.3</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>-19.5</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0.5</v>
+      </c>
+      <c r="I34">
+        <v>0.5</v>
+      </c>
+      <c r="J34">
+        <v>0.5</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C699678-DB96-45F7-AB32-C761E3144B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D287C116-80D6-4AE2-935D-20FA5FCA1A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="795" windowWidth="21600" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-14.2</v>
+        <v>-15</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-7</v>
+        <v>-6.5</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>-14.2</v>
+        <v>-15</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>-14.2</v>
+        <v>-11</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1843,6 +1843,129 @@
         <v>0</v>
       </c>
       <c r="M34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>-11</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0.5</v>
+      </c>
+      <c r="I35">
+        <v>0.5</v>
+      </c>
+      <c r="J35">
+        <v>0.5</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>-15</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0.5</v>
+      </c>
+      <c r="I36">
+        <v>0.5</v>
+      </c>
+      <c r="J36">
+        <v>0.5</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37">
+        <v>-3.5</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>-11</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0.5</v>
+      </c>
+      <c r="I37">
+        <v>0.5</v>
+      </c>
+      <c r="J37">
+        <v>0.5</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage4.xlsx
+++ b/Data/Excel/stage4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D287C116-80D6-4AE2-935D-20FA5FCA1A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59CCAC-8D0D-4D4A-AAB0-E82B9BED2CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="795" windowWidth="21600" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -498,7 +498,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>2.1</v>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="C3">
         <v>2.1</v>
@@ -586,7 +586,7 @@
         <v>2.1</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>2.1</v>
       </c>
       <c r="D5">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -662,19 +662,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-12.5</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>-6</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -867,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-15</v>
+        <v>-14.2</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>-4.5</v>
+        <v>-3</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>-15</v>
+        <v>-14.2</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1318,13 +1318,13 @@
         <v>16</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C22">
         <v>2.1</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>-14</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1441,13 +1441,13 @@
         <v>15</v>
       </c>
       <c r="B25">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1474,498 +1474,6 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26">
-        <v>6.5</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>19</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0.5</v>
-      </c>
-      <c r="I26">
-        <v>0.5</v>
-      </c>
-      <c r="J26">
-        <v>0.5</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27">
-        <v>-19</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>8</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0.5</v>
-      </c>
-      <c r="I27">
-        <v>0.5</v>
-      </c>
-      <c r="J27">
-        <v>0.5</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28">
-        <v>-19</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>18.5</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0.5</v>
-      </c>
-      <c r="I28">
-        <v>0.5</v>
-      </c>
-      <c r="J28">
-        <v>0.5</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29">
-        <v>-9</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>-19</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0.5</v>
-      </c>
-      <c r="I29">
-        <v>0.5</v>
-      </c>
-      <c r="J29">
-        <v>0.5</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30">
-        <v>8.1</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>-19.5</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0.5</v>
-      </c>
-      <c r="I30">
-        <v>0.5</v>
-      </c>
-      <c r="J30">
-        <v>0.5</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31">
-        <v>-18</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>-18</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0.5</v>
-      </c>
-      <c r="I31">
-        <v>0.5</v>
-      </c>
-      <c r="J31">
-        <v>0.5</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0.5</v>
-      </c>
-      <c r="I32">
-        <v>0.5</v>
-      </c>
-      <c r="J32">
-        <v>0.5</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>-11</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0.5</v>
-      </c>
-      <c r="I33">
-        <v>0.5</v>
-      </c>
-      <c r="J33">
-        <v>0.5</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34">
-        <v>11.3</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>-19.5</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0.5</v>
-      </c>
-      <c r="I34">
-        <v>0.5</v>
-      </c>
-      <c r="J34">
-        <v>0.5</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35">
-        <v>4</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>-11</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0.5</v>
-      </c>
-      <c r="I35">
-        <v>0.5</v>
-      </c>
-      <c r="J35">
-        <v>0.5</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36">
-        <v>2</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>-15</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0.5</v>
-      </c>
-      <c r="I36">
-        <v>0.5</v>
-      </c>
-      <c r="J36">
-        <v>0.5</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37">
-        <v>-3.5</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>-11</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0.5</v>
-      </c>
-      <c r="I37">
-        <v>0.5</v>
-      </c>
-      <c r="J37">
-        <v>0.5</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
         <v>0</v>
       </c>
     </row>
